--- a/Luban/Datas/Wave.xlsx
+++ b/Luban/Datas/Wave.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -817,219 +817,237 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
+      <c r="B17" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_01</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>level_01</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
+      <c r="B18" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_02</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>level_02</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
+      <c r="B19" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_03</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>level_03</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
+      <c r="B20" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_04</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>level_04</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
+      <c r="B21" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_05</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>level_05</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
+      <c r="B22" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_06</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>level_06</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
+      <c r="B23" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_07</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>level_07</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
+      <c r="B24" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_08</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>level_08</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
+      <c r="B25" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_09</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>level_09</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
+      <c r="B26" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_10</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>level_10</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
+      <c r="B27" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_11</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>level_11</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
+      <c r="B28" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_12</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>level_12</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>180</v>
+      <c r="E28" s="0" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Datas/Wave.xlsx
+++ b/Luban/Datas/Wave.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -1033,21 +1033,75 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
+      <c r="B29" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>level_01</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="0" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Datas/Wave.xlsx
+++ b/Luban/Datas/Wave.xlsx
@@ -923,6 +923,24 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
+    <x:row r="34">
+      <x:c r="B34" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C34" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">wave_level_01_spiral_045_sides</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">level_01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" t="n">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Luban/Datas/Wave.xlsx
+++ b/Luban/Datas/Wave.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_extra_planes_073</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_midboss_090</t>
+          <t>wave_level_01_enemy_08_test_002</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">

--- a/Luban/Datas/Wave.xlsx
+++ b/Luban/Datas/Wave.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -1039,6 +1039,24 @@
         <v>110</v>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/Wave.xlsx
+++ b/Luban/Datas/Wave.xlsx
@@ -2,10 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -23,30 +27,36 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="等线"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Arial"/>
-      <color rgb="00111827"/>
+      <family val="2"/>
+      <color rgb="FF111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00374151"/>
+      <family val="2"/>
+      <color rgb="FF374151"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="007A4B00"/>
+      <color rgb="FF7A4B00"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -58,35 +68,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E7EB"/>
+        <fgColor rgb="FFE5E7EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
@@ -101,25 +118,26 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1"/>
     <cellStyle name="Normal" xfId="2"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -333,6 +351,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -342,14 +362,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.84375" defaultRowHeight="14"/>
   <cols>
-    <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
-    <col width="22.33203125" customWidth="1" style="1" min="3" max="3"/>
-    <col width="16.33203125" customWidth="1" style="1" min="4" max="4"/>
-    <col width="12.33203125" customWidth="1" style="1" min="5" max="5"/>
-    <col width="8.83203125" customWidth="1" style="1" min="6" max="16384"/>
+    <col width="12.3046875" customWidth="1" style="1" min="1" max="2"/>
+    <col width="33.3828125" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="16.3046875" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12.3046875" customWidth="1" style="1" min="5" max="5"/>
+    <col width="8.84375" customWidth="1" style="1" min="6" max="6"/>
+    <col width="8.84375" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,7 +460,11 @@
           <t>wave_tutorial_001</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="n">
         <v>3</v>
       </c>
@@ -454,7 +479,11 @@
           <t>wave_tutorial_002</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
         <v>14</v>
       </c>
@@ -469,7 +498,11 @@
           <t>wave_tutorial_003</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
         <v>25</v>
       </c>
@@ -484,7 +517,11 @@
           <t>wave_battle_001</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="n">
         <v>36</v>
       </c>
@@ -499,7 +536,11 @@
           <t>wave_battle_002</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
         <v>52</v>
       </c>
@@ -514,7 +555,11 @@
           <t>wave_battle_003</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="n">
         <v>68</v>
       </c>
@@ -529,7 +574,11 @@
           <t>wave_battle_004</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="n">
         <v>84</v>
       </c>
@@ -544,7 +593,11 @@
           <t>wave_power_001</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="n">
         <v>96</v>
       </c>
@@ -559,7 +612,11 @@
           <t>wave_power_002</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="n">
         <v>112</v>
       </c>
@@ -574,7 +631,11 @@
           <t>wave_power_003</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="n">
         <v>128</v>
       </c>
@@ -589,7 +650,11 @@
           <t>wave_power_004</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n">
         <v>144</v>
       </c>
@@ -604,7 +669,11 @@
           <t>wave_transition_001</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="n">
         <v>152</v>
       </c>
@@ -619,442 +688,482 @@
           <t>wave_transition_002</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="n">
         <v>162</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="0" t="n">
+    <row r="17" ht="15.5" customHeight="1" s="6">
+      <c r="B17" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="C17" s="0" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" ht="15.5" customHeight="1" s="6">
+      <c r="B18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" ht="15.5" customHeight="1" s="6">
+      <c r="B19" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" ht="15.5" customHeight="1" s="6">
+      <c r="B20" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" ht="15.5" customHeight="1" s="6">
+      <c r="A21" s="0" t="n"/>
+      <c r="B21" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_spiral_030</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" ht="15.5" customHeight="1" s="6">
+      <c r="B22" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" ht="15.5" customHeight="1" s="6">
+      <c r="B23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" ht="15.5" customHeight="1" s="6">
+      <c r="B24" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" ht="15.5" customHeight="1" s="6">
+      <c r="B25" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" ht="15.5" customHeight="1" s="6">
+      <c r="B26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" ht="15.5" customHeight="1" s="6">
+      <c r="B27" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" ht="15.5" customHeight="1" s="6">
+      <c r="B28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_01_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" ht="15.5" customHeight="1" s="6">
+      <c r="B29" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_01</t>
         </is>
       </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E17" s="0" t="n">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>level_01</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
+    <row r="30" ht="15.5" customHeight="1" s="6">
+      <c r="B30" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_02</t>
         </is>
       </c>
-      <c r="D18" s="0" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>level_02</t>
         </is>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E30" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="C19" s="0" t="inlineStr">
+    <row r="31" ht="15.5" customHeight="1" s="6">
+      <c r="B31" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_03</t>
         </is>
       </c>
-      <c r="D19" s="0" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>level_03</t>
         </is>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E31" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
+    <row r="32" ht="15.5" customHeight="1" s="6">
+      <c r="B32" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_04</t>
         </is>
       </c>
-      <c r="D20" s="0" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>level_04</t>
         </is>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E32" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
+    <row r="33" ht="15.5" customHeight="1" s="6">
+      <c r="B33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_05</t>
         </is>
       </c>
-      <c r="D21" s="0" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>level_05</t>
         </is>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E33" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
+    <row r="34" ht="15.5" customHeight="1" s="6">
+      <c r="B34" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_06</t>
         </is>
       </c>
-      <c r="D22" s="0" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>level_06</t>
         </is>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E34" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="C23" s="0" t="inlineStr">
+    <row r="35" ht="15.5" customHeight="1" s="6">
+      <c r="B35" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_07</t>
         </is>
       </c>
-      <c r="D23" s="0" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>level_07</t>
         </is>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E35" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="C24" s="0" t="inlineStr">
+    <row r="36" ht="15.5" customHeight="1" s="6">
+      <c r="B36" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_08</t>
         </is>
       </c>
-      <c r="D24" s="0" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>level_08</t>
         </is>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E36" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="C25" s="0" t="inlineStr">
+    <row r="37" ht="15.5" customHeight="1" s="6">
+      <c r="B37" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_09</t>
         </is>
       </c>
-      <c r="D25" s="0" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>level_09</t>
         </is>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E37" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="0" t="n">
-        <v>23</v>
-      </c>
-      <c r="C26" s="0" t="inlineStr">
+    <row r="38" ht="15.5" customHeight="1" s="6">
+      <c r="B38" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_10</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>level_10</t>
         </is>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E38" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="C27" s="0" t="inlineStr">
+    <row r="39" ht="15.5" customHeight="1" s="6">
+      <c r="B39" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_11</t>
         </is>
       </c>
-      <c r="D27" s="0" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>level_11</t>
         </is>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E39" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="0" t="n">
-        <v>25</v>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
+    <row r="40" ht="15.5" customHeight="1" s="6">
+      <c r="B40" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_12</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>level_12</t>
         </is>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E40" s="0" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="0" t="n">
-        <v>26</v>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_resource_orbit</t>
-        </is>
-      </c>
-      <c r="D29" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E29" s="0" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="0" t="n">
-        <v>27</v>
-      </c>
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_resource_left_downright</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E30" s="0" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_resource_right_downleft</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E31" s="0" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="0" t="n">
-        <v>29</v>
-      </c>
-      <c r="C32" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_resource_top_down</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E32" s="0" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="n"/>
-      <c r="B33" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="C33" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_spiral_030</t>
-        </is>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E33" s="0" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="0" t="n">
-        <v>31</v>
-      </c>
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_spiral_045_sides</t>
-        </is>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E34" s="0" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="0" t="n">
-        <v>32</v>
-      </c>
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_resource_heal_070</t>
-        </is>
-      </c>
-      <c r="D35" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E35" s="0" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="0" t="n">
-        <v>33</v>
-      </c>
-      <c r="C36" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_side_helis_073</t>
-        </is>
-      </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E36" s="0" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="0" t="n">
-        <v>34</v>
-      </c>
-      <c r="C37" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_homing_fighters_080</t>
-        </is>
-      </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E37" s="0" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="C38" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_enemy_08_test_002</t>
-        </is>
-      </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E38" s="0" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="0" t="n">
-        <v>36</v>
-      </c>
-      <c r="C39" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_side_helis_110</t>
-        </is>
-      </c>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E39" s="0" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="0" t="n">
-        <v>37</v>
-      </c>
-      <c r="C40" s="0" t="inlineStr">
-        <is>
-          <t>wave_level_01_split_fighters_130</t>
-        </is>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t>level_01</t>
-        </is>
-      </c>
-      <c r="E40" s="0" t="n">
-        <v>130</v>
+    <row r="41">
+      <c r="B41" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_left_downright_003</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_orbit_downleft_009</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Datas/Wave.xlsx
+++ b/Luban/Datas/Wave.xlsx
@@ -362,7 +362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.84375" defaultRowHeight="14"/>
   <cols>
     <col width="12.3046875" customWidth="1" style="1" min="1" max="2"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>wave_level_02_resource2_left_downright_003</t>
+          <t>wave_level_02_helicopter_top_002</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E41" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>wave_level_02_resource2_orbit_downleft_009</t>
+          <t>wave_level_02_resource2_right_arc_005</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1163,7 +1163,133 @@
         </is>
       </c>
       <c r="E42" s="0" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_left_arc_010</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>41</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_n_left_014</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>42</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_n_right_019</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>43</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_w_top_022</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>44</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_l_left_028</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>45</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_l_right_032</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>46</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>wave_level_02_helicopter_top_036</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Datas/Wave.xlsx
+++ b/Luban/Datas/Wave.xlsx
@@ -362,7 +362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E299"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.84375" defaultRowHeight="14"/>
   <cols>
     <col width="12.3046875" customWidth="1" style="1" min="1" max="2"/>
@@ -698,6 +698,7 @@
       </c>
     </row>
     <row r="17" ht="15.5" customHeight="1" s="6">
+      <c r="A17" s="2" t="n"/>
       <c r="B17" s="2" t="n">
         <v>14</v>
       </c>
@@ -711,11 +712,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="2" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1" s="6">
+      <c r="A18" s="2" t="n"/>
       <c r="B18" s="2" t="n">
         <v>15</v>
       </c>
@@ -729,11 +731,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="15.5" customHeight="1" s="6">
+      <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="n">
         <v>16</v>
       </c>
@@ -747,11 +750,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="2" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="20" ht="15.5" customHeight="1" s="6">
+      <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="n">
         <v>17</v>
       </c>
@@ -765,12 +769,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1" s="6">
-      <c r="A21" s="0" t="n"/>
+      <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="n">
         <v>18</v>
       </c>
@@ -784,11 +788,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="2" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="22" ht="15.5" customHeight="1" s="6">
+      <c r="A22" s="2" t="n"/>
       <c r="B22" s="2" t="n">
         <v>19</v>
       </c>
@@ -802,11 +807,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="2" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="23" ht="15.5" customHeight="1" s="6">
+      <c r="A23" s="2" t="n"/>
       <c r="B23" s="2" t="n">
         <v>20</v>
       </c>
@@ -820,11 +826,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="2" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="24" ht="15.5" customHeight="1" s="6">
+      <c r="A24" s="2" t="n"/>
       <c r="B24" s="2" t="n">
         <v>21</v>
       </c>
@@ -838,11 +845,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="2" t="n">
         <v>73</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1" s="6">
+      <c r="A25" s="2" t="n"/>
       <c r="B25" s="2" t="n">
         <v>22</v>
       </c>
@@ -856,11 +864,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="2" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1" s="6">
+      <c r="A26" s="2" t="n"/>
       <c r="B26" s="2" t="n">
         <v>23</v>
       </c>
@@ -874,11 +883,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="2" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1" s="6">
+      <c r="A27" s="2" t="n"/>
       <c r="B27" s="2" t="n">
         <v>24</v>
       </c>
@@ -892,11 +902,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="2" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1" s="6">
+      <c r="A28" s="2" t="n"/>
       <c r="B28" s="2" t="n">
         <v>25</v>
       </c>
@@ -910,11 +921,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="2" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="29" ht="15.5" customHeight="1" s="6">
+      <c r="A29" s="2" t="n"/>
       <c r="B29" s="2" t="n">
         <v>26</v>
       </c>
@@ -928,11 +940,12 @@
           <t>level_01</t>
         </is>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="2" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1" s="6">
+      <c r="A30" s="2" t="n"/>
       <c r="B30" s="2" t="n">
         <v>27</v>
       </c>
@@ -946,350 +959,5119 @@
           <t>level_02</t>
         </is>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="2" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1" s="6">
+      <c r="A31" s="2" t="n"/>
       <c r="B31" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_helicopter_top_002</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" ht="15.5" customHeight="1" s="6">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_right_arc_005</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" ht="15.5" customHeight="1" s="6">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_left_arc_010</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" ht="15.5" customHeight="1" s="6">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_n_left_014</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" ht="15.5" customHeight="1" s="6">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_n_right_019</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" ht="15.5" customHeight="1" s="6">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_w_top_022</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" ht="15.5" customHeight="1" s="6">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_l_left_028</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+    </row>
+    <row r="38" ht="15.5" customHeight="1" s="6">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_resource2_l_right_032</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" ht="15.5" customHeight="1" s="6">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_02_helicopter_top_036</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" ht="15.5" customHeight="1" s="6">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_tutorial_001</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_tutorial_002</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_tutorial_003</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_battle_001</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_battle_002</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_battle_003</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_battle_004</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_power_001</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_power_002</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_power_003</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_power_004</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_transition_001</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_transition_002</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_spiral_030</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_03_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_03</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>level_03</t>
         </is>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E65" s="2" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="32" ht="15.5" customHeight="1" s="6">
-      <c r="B32" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_tutorial_001</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_tutorial_002</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_tutorial_003</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_battle_001</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_battle_002</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_battle_003</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_battle_004</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_power_001</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_power_002</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_power_003</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_power_004</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_transition_001</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_transition_002</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_spiral_030</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_04_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_04</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>level_04</t>
         </is>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E91" s="2" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="33" ht="15.5" customHeight="1" s="6">
-      <c r="B33" s="2" t="n">
+    <row r="92">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_tutorial_001</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_tutorial_002</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_tutorial_003</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_battle_001</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_battle_002</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_battle_003</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_battle_004</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_power_001</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_power_002</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_power_003</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_power_004</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_transition_001</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_transition_002</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_spiral_030</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_05_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_05</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>level_05</t>
         </is>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E117" s="2" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="34" ht="15.5" customHeight="1" s="6">
-      <c r="B34" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_tutorial_001</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_tutorial_002</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_tutorial_003</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_battle_001</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n"/>
+      <c r="B122" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_battle_002</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_battle_003</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_battle_004</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_power_001</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n"/>
+      <c r="B126" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_power_002</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_power_003</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_power_004</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_transition_001</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_transition_002</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n"/>
+      <c r="B131" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n"/>
+      <c r="B132" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n"/>
+      <c r="B135" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_spiral_030</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n"/>
+      <c r="B136" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n"/>
+      <c r="B138" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_06_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>level_06</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_06</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>level_06</t>
         </is>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E143" s="2" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="35" ht="15.5" customHeight="1" s="6">
-      <c r="B35" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_tutorial_001</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_tutorial_002</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n"/>
+      <c r="B146" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_tutorial_003</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_battle_001</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_battle_002</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n"/>
+      <c r="B149" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_battle_003</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n"/>
+      <c r="B150" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_battle_004</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n"/>
+      <c r="B151" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_power_001</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_power_002</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n"/>
+      <c r="B153" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_power_003</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n"/>
+      <c r="B154" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_power_004</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_transition_001</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_transition_002</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n"/>
+      <c r="B157" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_spiral_030</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_07_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>level_07</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_07</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>level_07</t>
         </is>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E169" s="2" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="36" ht="15.5" customHeight="1" s="6">
-      <c r="B36" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_tutorial_001</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n"/>
+      <c r="B171" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_tutorial_002</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_tutorial_003</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_battle_001</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_battle_002</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_battle_003</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n"/>
+      <c r="B176" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_battle_004</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n"/>
+      <c r="B177" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_power_001</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_power_002</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_power_003</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_power_004</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_transition_001</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_transition_002</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n"/>
+      <c r="B186" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n"/>
+      <c r="B187" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_spiral_030</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n"/>
+      <c r="B188" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n"/>
+      <c r="B189" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n"/>
+      <c r="B190" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n"/>
+      <c r="B191" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_08_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>level_08</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n"/>
+      <c r="B195" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_08</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>level_08</t>
         </is>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E195" s="2" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="37" ht="15.5" customHeight="1" s="6">
-      <c r="B37" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="n"/>
+      <c r="B196" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_tutorial_001</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n"/>
+      <c r="B197" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_tutorial_002</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_tutorial_003</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_battle_001</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_battle_002</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n"/>
+      <c r="B201" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_battle_003</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n"/>
+      <c r="B202" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_battle_004</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n"/>
+      <c r="B203" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_power_001</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n"/>
+      <c r="B204" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_power_002</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n"/>
+      <c r="B205" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_power_003</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n"/>
+      <c r="B206" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_power_004</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n"/>
+      <c r="B207" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_transition_001</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n"/>
+      <c r="B208" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_transition_002</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n"/>
+      <c r="B209" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n"/>
+      <c r="B210" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n"/>
+      <c r="B211" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n"/>
+      <c r="B212" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n"/>
+      <c r="B213" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_spiral_030</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n"/>
+      <c r="B214" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n"/>
+      <c r="B215" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n"/>
+      <c r="B216" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n"/>
+      <c r="B217" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n"/>
+      <c r="B218" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n"/>
+      <c r="B219" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n"/>
+      <c r="B220" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_09_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>level_09</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n"/>
+      <c r="B221" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_09</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>level_09</t>
         </is>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E221" s="2" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="38" ht="15.5" customHeight="1" s="6">
-      <c r="B38" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="n"/>
+      <c r="B222" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_tutorial_001</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n"/>
+      <c r="B223" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_tutorial_002</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n"/>
+      <c r="B224" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_tutorial_003</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n"/>
+      <c r="B225" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_battle_001</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n"/>
+      <c r="B226" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_battle_002</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n"/>
+      <c r="B227" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_battle_003</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n"/>
+      <c r="B228" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_battle_004</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n"/>
+      <c r="B229" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_power_001</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n"/>
+      <c r="B230" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_power_002</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n"/>
+      <c r="B231" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_power_003</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n"/>
+      <c r="B232" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_power_004</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n"/>
+      <c r="B233" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_transition_001</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n"/>
+      <c r="B234" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_transition_002</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n"/>
+      <c r="B235" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n"/>
+      <c r="B236" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n"/>
+      <c r="B237" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n"/>
+      <c r="B238" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n"/>
+      <c r="B239" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_spiral_030</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n"/>
+      <c r="B240" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n"/>
+      <c r="B241" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n"/>
+      <c r="B242" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n"/>
+      <c r="B243" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n"/>
+      <c r="B244" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n"/>
+      <c r="B245" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n"/>
+      <c r="B246" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_10_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>level_10</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n"/>
+      <c r="B247" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_10</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>level_10</t>
         </is>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E247" s="2" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="39" ht="15.5" customHeight="1" s="6">
-      <c r="B39" s="2" t="n">
+    <row r="248">
+      <c r="A248" s="2" t="n"/>
+      <c r="B248" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_tutorial_001</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n"/>
+      <c r="B249" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_tutorial_002</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n"/>
+      <c r="B250" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_tutorial_003</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n"/>
+      <c r="B251" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_battle_001</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n"/>
+      <c r="B252" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_battle_002</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n"/>
+      <c r="B253" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_battle_003</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n"/>
+      <c r="B254" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_battle_004</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n"/>
+      <c r="B255" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_power_001</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n"/>
+      <c r="B256" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_power_002</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n"/>
+      <c r="B257" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_power_003</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n"/>
+      <c r="B258" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_power_004</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n"/>
+      <c r="B259" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_transition_001</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n"/>
+      <c r="B260" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_transition_002</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n"/>
+      <c r="B261" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n"/>
+      <c r="B262" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n"/>
+      <c r="B263" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n"/>
+      <c r="B264" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n"/>
+      <c r="B265" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_spiral_030</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n"/>
+      <c r="B266" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n"/>
+      <c r="B267" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n"/>
+      <c r="B268" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n"/>
+      <c r="B269" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n"/>
+      <c r="B270" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n"/>
+      <c r="B271" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n"/>
+      <c r="B272" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_11_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>level_11</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n"/>
+      <c r="B273" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_11</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>level_11</t>
         </is>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E273" s="2" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="40" ht="15.5" customHeight="1" s="6">
-      <c r="B40" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="2" t="n"/>
+      <c r="B274" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_tutorial_001</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n"/>
+      <c r="B275" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_tutorial_002</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n"/>
+      <c r="B276" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_tutorial_003</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n"/>
+      <c r="B277" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_battle_001</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n"/>
+      <c r="B278" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_battle_002</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n"/>
+      <c r="B279" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_battle_003</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n"/>
+      <c r="B280" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_battle_004</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n"/>
+      <c r="B281" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_power_001</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n"/>
+      <c r="B282" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_power_002</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n"/>
+      <c r="B283" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_power_003</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n"/>
+      <c r="B284" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_power_004</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n"/>
+      <c r="B285" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_transition_001</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n"/>
+      <c r="B286" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_transition_002</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n"/>
+      <c r="B287" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_resource_orbit</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n"/>
+      <c r="B288" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n"/>
+      <c r="B289" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n"/>
+      <c r="B290" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_resource_top_down</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n"/>
+      <c r="B291" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_spiral_030</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n"/>
+      <c r="B292" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n"/>
+      <c r="B293" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_resource_heal_070</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n"/>
+      <c r="B294" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_side_helis_073</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n"/>
+      <c r="B295" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_homing_fighters_080</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n"/>
+      <c r="B296" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_enemy_08_test_002</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n"/>
+      <c r="B297" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_side_helis_110</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n"/>
+      <c r="B298" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>wave_level_12_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>level_12</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n"/>
+      <c r="B299" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
         <is>
           <t>wave_boss_final_12</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D299" s="2" t="inlineStr">
         <is>
           <t>level_12</t>
         </is>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E299" s="2" t="n">
         <v>180</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>wave_level_02_helicopter_top_002</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>level_02</t>
-        </is>
-      </c>
-      <c r="E41" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>wave_level_02_resource2_right_arc_005</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>level_02</t>
-        </is>
-      </c>
-      <c r="E42" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="n">
-        <v>40</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>wave_level_02_resource2_left_arc_010</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>level_02</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="n">
-        <v>41</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>wave_level_02_resource2_n_left_014</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>level_02</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="n">
-        <v>42</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>wave_level_02_resource2_n_right_019</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>level_02</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="n">
-        <v>43</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>wave_level_02_resource2_w_top_022</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>level_02</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="n">
-        <v>44</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>wave_level_02_resource2_l_left_028</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>level_02</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="n">
-        <v>45</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>wave_level_02_resource2_l_right_032</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>level_02</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="n">
-        <v>46</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>wave_level_02_helicopter_top_036</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>level_02</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Datas/Wave.xlsx
+++ b/Luban/Datas/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R3fcd16441f28431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="Rb04dfd6378e640f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6046,6 +6046,36 @@
         <x:v>105</x:v>
       </x:c>
     </x:row>
+    <x:row r="300">
+      <x:c r="A300"/>
+      <x:c r="B300" t="n">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="C300" t="str">
+        <x:v>wave_level_02_single_shot_fighters_038</x:v>
+      </x:c>
+      <x:c r="D300" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E300" t="n">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301"/>
+      <x:c r="B301" t="n">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="C301" t="str">
+        <x:v>wave_level_02_single_shot_fighters_042</x:v>
+      </x:c>
+      <x:c r="D301" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E301" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
